--- a/17_Real_Estate_REIT/instances/public_wework_2022_stress.xlsx
+++ b/17_Real_Estate_REIT/instances/public_wework_2022_stress.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -38,7 +38,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="222">
   <si>
-    <t xml:space="preserve">[PROPERTY/REIT] — Real Estate Model</t>
+    <t xml:space="preserve">WeWork 2022 occupancy-economics and refinancing stress proxy</t>
   </si>
   <si>
     <t xml:space="preserve">Property type:</t>
@@ -708,7 +708,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
@@ -716,7 +716,6 @@
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0\x"/>
     <numFmt numFmtId="170" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="171" formatCode="General"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -793,6 +792,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -804,13 +810,6 @@
       <i val="true"/>
       <sz val="8"/>
       <color rgb="FF808080"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -912,36 +911,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -949,7 +944,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -957,107 +952,107 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1141,34 +1136,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1314,55 +1309,55 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C7"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1376,20 +1371,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E23"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
         <v>163</v>
       </c>
@@ -1403,150 +1398,150 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="29" t="n">
         <f aca="false">'Property Pro Forma'!C11-('Property Pro Forma'!C5-'Property Pro Forma'!C6+'Property Pro Forma'!C8-'Property Pro Forma'!C10)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="30" t="str">
+      <c r="D5" s="29" t="str">
         <f aca="false">IF(ABS(C5)&lt;0.01,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="29" t="n">
         <f aca="false">'REIT FFO-AFFO'!C7-('REIT FFO-AFFO'!C4+'REIT FFO-AFFO'!C5-'REIT FFO-AFFO'!C6)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="30" t="str">
+      <c r="D6" s="29" t="str">
         <f aca="false">IF(ABS(C6)&lt;0.01,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="29" t="n">
         <f aca="false">'REIT FFO-AFFO'!C11-('REIT FFO-AFFO'!C7-'REIT FFO-AFFO'!C9-'REIT FFO-AFFO'!C10)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="30" t="str">
+      <c r="D7" s="29" t="str">
         <f aca="false">IF(ABS(C7)&lt;0.01,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="29" t="n">
         <f aca="false">MIN('Debt Schedule'!I8:I12)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="30" t="str">
+      <c r="D8" s="29" t="str">
         <f aca="false">IF(C8&gt;='Debt Schedule'!C5,"PASS",IF(C8&gt;=1,"REVIEW","BREACH"))</f>
         <v>BREACH</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="30" t="n">
-        <f aca="false">IFERROR('Cap Rate &amp; Valuation'!C10/'Cap Rate &amp; Valuation'!C8,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="30" t="str">
-        <f aca="false">IF(C9&lt;=0.75,"PASS",IF(C9&lt;=0.85,"REVIEW","BREACH"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="C9" s="29" t="str">
+        <f aca="false">IFERROR('Cap Rate &amp; Valuation'!C10/'Cap Rate &amp; Valuation'!C8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D9" s="29" t="str">
+        <f aca="false">IF(ISNUMBER(C9),IF(C9&lt;=0.75,"PASS",IF(C9&lt;=0.85,"REVIEW","BREACH")),"REVIEW")</f>
+        <v>REVIEW</v>
+      </c>
+      <c r="E9" s="0" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="29" t="n">
         <f aca="false">MIN('Lease Roll'!K5:K9)</f>
         <v>0.96875</v>
       </c>
-      <c r="D10" s="30" t="str">
+      <c r="D10" s="29" t="str">
         <f aca="false">IF(C10&gt;=0.9,"PASS",IF(C10&gt;=0.8,"REVIEW","BREACH"))</f>
         <v>PASS</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="0" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>178</v>
       </c>
       <c r="C11" s="21" t="n">
         <f aca="false">'Property Pro Forma'!C14</f>
         <v>-2109.25</v>
       </c>
-      <c r="D11" s="30" t="str">
+      <c r="D11" s="29" t="str">
         <f aca="false">IF(C11&gt;=0,"PASS","BREACH")</f>
         <v>BREACH</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="0" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="29" t="n">
         <f aca="false">IF(AND(ISNUMBER('5-Year Hold &amp; IRR'!C6),ISNUMBER('Cap Rate &amp; Valuation'!C9)),'5-Year Hold &amp; IRR'!C6-'Cap Rate &amp; Valuation'!C9,0)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="30" t="str">
+      <c r="D12" s="29" t="str">
         <f aca="false">IF(AND(ISNUMBER('5-Year Hold &amp; IRR'!C6),ISNUMBER('Cap Rate &amp; Valuation'!C9)),IF(C12&gt;=0,"PASS","REVIEW"),"REVIEW")</f>
         <v>REVIEW</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="0" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="31" t="str">
+      <c r="C14" s="30" t="str">
         <f aca="false">IF(COUNTIF(D5:D12,"FAIL")+COUNTIF(D5:D12,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D12,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v>BREACH</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="32" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="31" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
         <v>147</v>
       </c>
       <c r="C17" s="21" t="n">
@@ -1554,8 +1549,8 @@
         <v>-2109.25</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
         <v>184</v>
       </c>
       <c r="C18" s="22" t="str">
@@ -1563,8 +1558,8 @@
         <v>-</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
         <v>185</v>
       </c>
       <c r="C19" s="22" t="str">
@@ -1572,17 +1567,17 @@
         <v>-</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="27" t="str">
+      <c r="C20" s="26" t="str">
         <f aca="false">'5-Year Hold &amp; IRR'!C28</f>
         <v>-</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
         <v>187</v>
       </c>
       <c r="C21" s="21" t="n">
@@ -1590,8 +1585,8 @@
         <v>-2034</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
         <v>188</v>
       </c>
       <c r="C22" s="21" t="n">
@@ -1599,8 +1594,8 @@
         <v>-2034</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
         <v>146</v>
       </c>
       <c r="C23" s="21" t="n">
@@ -1611,7 +1606,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1625,66 +1620,66 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:H28"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="32" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="31" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="19" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>192</v>
       </c>
       <c r="C6" s="19" t="n">
         <v>0.065</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="32" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="16" t="n">
         <f aca="false">IFERROR(ABS('Property Pro Forma'!C13),"-")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="16" t="n">
         <f aca="false">IFERROR('Cap Rate &amp; Valuation'!C8-'Cap Rate &amp; Valuation'!C10,"-")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="17" t="s">
         <v>196</v>
       </c>
@@ -1701,11 +1696,11 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>147</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="16" t="n">
         <f aca="false">'Property Pro Forma'!C11</f>
         <v>-2109.25</v>
       </c>
@@ -1726,8 +1721,8 @@
         <v>-2283.12003348</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
         <v>145</v>
       </c>
       <c r="C14" s="21" t="n">
@@ -1751,8 +1746,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
         <v>201</v>
       </c>
       <c r="C15" s="21" t="n">
@@ -1776,38 +1771,38 @@
         <v>-2283.12003348</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="C16" s="34" t="n">
+      <c r="C16" s="33" t="n">
         <f aca="false">IFERROR(C13/C14,0)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D16" s="33" t="n">
         <f aca="false">IFERROR(D13/D14,0)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E16" s="33" t="n">
         <f aca="false">IFERROR(E13/E14,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="33" t="n">
         <f aca="false">IFERROR(F13/F14,0)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="34" t="n">
+      <c r="G16" s="33" t="n">
         <f aca="false">IFERROR(G13/G14,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="32" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="31" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
         <v>204</v>
       </c>
       <c r="C19" s="21" t="n">
@@ -1815,8 +1810,8 @@
         <v>-2328.7824341496</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
         <v>205</v>
       </c>
       <c r="C20" s="21" t="n">
@@ -1824,8 +1819,8 @@
         <v>-35827.42206384</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
         <v>206</v>
       </c>
       <c r="C21" s="21" t="n">
@@ -1833,26 +1828,26 @@
         <v>716.5484412768</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="24" t="n">
+      <c r="C22" s="16" t="n">
         <f aca="false">-'Debt Schedule'!G12</f>
         <v>-0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="15" t="n">
         <f aca="false">C20+C21+C22</f>
         <v>-35110.8736225632</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32"/>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="31"/>
       <c r="C25" s="17" t="s">
         <v>209</v>
       </c>
@@ -1872,8 +1867,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="s">
         <v>210</v>
       </c>
       <c r="C26" s="21" t="n">
@@ -1901,20 +1896,20 @@
         <v>-37393.9936560432</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="1" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="C27" s="35" t="str">
+      <c r="C27" s="34" t="str">
         <f aca="false">IFERROR(IRR(C26:H26),"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="1" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="C28" s="36" t="str">
+      <c r="C28" s="35" t="str">
         <f aca="false">IFERROR(SUM(D26:H26)/C9,"-")</f>
         <v>-</v>
       </c>
@@ -1922,7 +1917,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1936,21 +1931,21 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
         <v>80</v>
       </c>
@@ -1967,90 +1962,90 @@
         <v>216</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="29" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2064,638 +2059,638 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F63"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="9" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10" t="s">
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="9" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="1" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="1" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="1" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="1" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="9" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="10" t="s">
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="1" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="1" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="1" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="1" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="9" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="10" t="s">
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="1" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="1" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="1" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="1" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="1" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="9" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="10" t="s">
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="1" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="1" t="n">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="1" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="1" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="1" t="n">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="9" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="10" t="s">
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F61" s="10" t="s">
+      <c r="F61" s="9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="1" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="0" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="1" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="0" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2745,7 +2740,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2759,230 +2754,230 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I54"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H23" s="11"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H25" s="11"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H29" s="11"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H35" s="11"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H39" s="11"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H40" s="11"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H41" s="11"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H42" s="11"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H43" s="11"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H44" s="11"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H45" s="11"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H46" s="11"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H47" s="11"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H48" s="11"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H49" s="11"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H50" s="11"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H51" s="11"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H52" s="11"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H53" s="11"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H54" s="11"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="10"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="10"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="10"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="10"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="10"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="10"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="10"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="10"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H46" s="10"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="10"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="10"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="10"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H50" s="10"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="10"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H52" s="10"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="10"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3000,7 +2995,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3014,212 +3009,212 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J40"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J23" s="11"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J24" s="11"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J25" s="11"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J29" s="11"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J33" s="11"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J35" s="11"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J39" s="11"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J40" s="11"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J34" s="10"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J36" s="10"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J38" s="10"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J39" s="10"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3233,7 +3228,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3247,99 +3242,99 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="12" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>3245</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="12" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="12" t="s">
+      <c r="C6" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">C5-C6</f>
         <v>3245</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="12" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
+      <c r="C8" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="15" t="n">
         <f aca="false">C7+C8</f>
         <v>3245</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="12" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="12" t="n">
         <v>5354.25</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <f aca="false">C9-C10</f>
         <v>-2109.25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C12" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+      <c r="C12" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="16" t="n">
         <f aca="false">'Debt Schedule'!E8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="3" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="15" t="n">
         <f aca="false">C11-C12-C13</f>
         <v>-2109.25</v>
       </c>
@@ -3347,7 +3342,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3361,25 +3356,25 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:K12"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="17" t="s">
         <v>119</v>
       </c>
@@ -3411,8 +3406,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="18" t="n">
@@ -3448,8 +3443,8 @@
         <v>0.9775</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="18" t="n">
@@ -3485,8 +3480,8 @@
         <v>0.975</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="18" t="n">
@@ -3522,8 +3517,8 @@
         <v>0.9725</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="18" t="n">
@@ -3559,8 +3554,8 @@
         <v>0.9775</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="18" t="n">
@@ -3596,7 +3591,7 @@
         <v>0.96875</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="23" t="s">
         <v>129</v>
       </c>
@@ -3604,7 +3599,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3618,55 +3613,55 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C11"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="16" t="n">
         <f aca="false">'Property Pro Forma'!C11</f>
         <v>-2109.25</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>132</v>
       </c>
       <c r="C5" s="19" t="n">
         <v>0.06</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="15" t="n">
         <f aca="false">IFERROR(C4/C5,"-")</f>
         <v>-35154.1666666667</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+      <c r="C8" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>135</v>
       </c>
       <c r="C9" s="22" t="str">
@@ -3674,16 +3669,16 @@
         <v>-</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+      <c r="C10" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>137</v>
       </c>
       <c r="C11" s="22" t="str">
@@ -3694,7 +3689,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3708,46 +3703,46 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J12"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C3" s="19" t="n">
         <v>0.06</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="24" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="25" t="n">
         <v>1.25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="17" t="s">
         <v>119</v>
       </c>
@@ -3776,8 +3771,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="21" t="n">
@@ -3804,17 +3799,17 @@
         <f aca="false">'5-Year Hold &amp; IRR'!C13</f>
         <v>-2109.25</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="26" t="n">
         <f aca="false">IFERROR(H8/E8,0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="27" t="n">
+      <c r="J8" s="26" t="n">
         <f aca="false">I8-$C$5</f>
         <v>-1.25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="21" t="n">
@@ -3841,17 +3836,17 @@
         <f aca="false">'5-Year Hold &amp; IRR'!D13</f>
         <v>-2151.435</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="26" t="n">
         <f aca="false">IFERROR(H9/E9,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J9" s="26" t="n">
         <f aca="false">I9-$C$5</f>
         <v>-1.25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="n">
         <v>3</v>
       </c>
       <c r="C10" s="21" t="n">
@@ -3878,17 +3873,17 @@
         <f aca="false">'5-Year Hold &amp; IRR'!E13</f>
         <v>-2194.4637</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="26" t="n">
         <f aca="false">IFERROR(H10/E10,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="27" t="n">
+      <c r="J10" s="26" t="n">
         <f aca="false">I10-$C$5</f>
         <v>-1.25</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="n">
         <v>4</v>
       </c>
       <c r="C11" s="21" t="n">
@@ -3915,17 +3910,17 @@
         <f aca="false">'5-Year Hold &amp; IRR'!F13</f>
         <v>-2238.352974</v>
       </c>
-      <c r="I11" s="27" t="n">
+      <c r="I11" s="26" t="n">
         <f aca="false">IFERROR(H11/E11,0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="27" t="n">
+      <c r="J11" s="26" t="n">
         <f aca="false">I11-$C$5</f>
         <v>-1.25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="n">
         <v>5</v>
       </c>
       <c r="C12" s="21" t="n">
@@ -3952,11 +3947,11 @@
         <f aca="false">'5-Year Hold &amp; IRR'!G13</f>
         <v>-2283.12003348</v>
       </c>
-      <c r="I12" s="27" t="n">
+      <c r="I12" s="26" t="n">
         <f aca="false">IFERROR(H12/E12,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="27" t="n">
+      <c r="J12" s="26" t="n">
         <f aca="false">I12-$C$5</f>
         <v>-1.25</v>
       </c>
@@ -3964,7 +3959,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3978,73 +3973,73 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D15"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="1" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="12" t="n">
         <v>-2034</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="C5" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="C6" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="15" t="n">
         <f aca="false">C4+C5-C6</f>
         <v>-2034</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+      <c r="C9" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+      <c r="C10" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="15" t="n">
         <f aca="false">C7-C9-C10</f>
         <v>-2034</v>
       </c>
@@ -4052,28 +4047,28 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="27" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="28" t="n">
         <f aca="false">IFERROR(C7/C13,"-")</f>
         <v>-2034</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="28" t="n">
         <f aca="false">IFERROR(C11/C13,"-")</f>
         <v>-2034</v>
       </c>
@@ -4081,7 +4076,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
